--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-09T08:13:21.409Z</t>
+    <t>2026-07-09T12:22:44.342Z</t>
   </si>
   <si>
     <t>Steel Supplier &amp; Manufacturer in India | Tata Steel</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-09T12:22:44.342Z</t>
+    <t>2026-07-10T04:40:17.679Z</t>
   </si>
   <si>
     <t>Steel Supplier &amp; Manufacturer in India | Tata Steel</t>
